--- a/car/caragenina_data.xlsx
+++ b/car/caragenina_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trevo\OneDrive\Documents\GitHub\TEdissy_analysis\car\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7AAD7F5-7964-4202-BF15-AEE929E686F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E5E8942-44DB-460E-ACC8-9B4340B1677B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1177,7 +1177,7 @@
         <v>1.1027</v>
       </c>
       <c r="M9" s="5">
-        <f t="shared" si="1"/>
+        <f>L9/D9</f>
         <v>0.22035930536959691</v>
       </c>
     </row>
